--- a/artfynd/A 21183-2025 artfynd.xlsx
+++ b/artfynd/A 21183-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>451555</v>
       </c>
       <c r="B2" t="n">
-        <v>98153</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>101003</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -729,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>800846.5301115282</v>
+        <v>800847</v>
       </c>
       <c r="R2" t="n">
-        <v>7610372.396660057</v>
+        <v>7610372</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -762,19 +757,9 @@
           <t>2002-08-05</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2002-08-05</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -804,6 +789,216 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>98614390</v>
+      </c>
+      <c r="B3" t="n">
+        <v>96056</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>2265</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Kärrtrumpetmossa</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Tayloria lingulata</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Dicks.) Lindb.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Onkanharju, vid södra sidan av Mounioälven (W961), T lm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>800815</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7610386</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Karesuando</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2021-08-15</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2021-08-15</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>älvstrand</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Niklas Lönnell</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Niklas Lönnell, Peter Ståhl</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>95502626</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58116</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103022</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Lappmes</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Poecile cinctus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Boddaert, 1783)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Onkanharju, T lm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>800465</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7609827</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Karesuando</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2021-08-15</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2021-08-15</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Niklas Lönnell</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Niklas Lönnell, Peter Ståhl</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 21183-2025 artfynd.xlsx
+++ b/artfynd/A 21183-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -780,6 +785,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95502626</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -897,6 +907,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/451555</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -999,8 +1014,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98614390</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>